--- a/data/mini-example-resilience/Power_Demand.xlsx
+++ b/data/mini-example-resilience/Power_Demand.xlsx
@@ -5,17 +5,30 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\Mini-example-resilience\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28EBDC0-E457-4B5B-A583-B751F1714435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175883D3-FBBB-4B29-984D-62CA3C2D5536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -100,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="56">
   <si>
     <t>Power - Demand</t>
   </si>
@@ -265,12 +278,18 @@
   </si>
   <si>
     <t>TestSource1</t>
+  </si>
+  <si>
+    <t>Node_feedin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -361,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -393,6 +412,9 @@
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1165,109 +1187,165 @@
       <c r="F8" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="14">
-        <v>574.27430000000004</v>
-      </c>
-      <c r="H8" s="14">
-        <v>528.10990000000004</v>
-      </c>
-      <c r="I8" s="14">
-        <v>494.47</v>
-      </c>
-      <c r="J8" s="14">
-        <v>474.04739999999998</v>
-      </c>
-      <c r="K8" s="14">
-        <v>461.03190000000001</v>
-      </c>
-      <c r="L8" s="14">
-        <v>457.03750000000002</v>
-      </c>
-      <c r="M8" s="14">
-        <v>478.04489999999998</v>
-      </c>
-      <c r="N8" s="14">
-        <v>518.34860000000003</v>
-      </c>
-      <c r="O8" s="14">
-        <v>567.35569999999996</v>
-      </c>
-      <c r="P8" s="14">
-        <v>593.11770000000001</v>
-      </c>
-      <c r="Q8" s="14">
-        <v>623.15359999999998</v>
-      </c>
-      <c r="R8" s="14">
-        <v>628.95500000000004</v>
-      </c>
-      <c r="S8" s="14">
-        <v>626.21410000000003</v>
-      </c>
-      <c r="T8" s="14">
-        <v>620.56060000000002</v>
-      </c>
-      <c r="U8" s="14">
-        <v>598.04229999999995</v>
-      </c>
-      <c r="V8" s="14">
-        <v>588.49530000000004</v>
-      </c>
-      <c r="W8" s="14">
-        <v>588.61760000000004</v>
-      </c>
-      <c r="X8" s="14">
-        <v>608.88480000000004</v>
-      </c>
-      <c r="Y8" s="14">
-        <v>663.42909999999995</v>
-      </c>
-      <c r="Z8" s="14">
-        <v>672.60519999999997</v>
-      </c>
-      <c r="AA8" s="14">
-        <v>669.38459999999998</v>
-      </c>
-      <c r="AB8" s="14">
-        <v>661.28869999999995</v>
-      </c>
-      <c r="AC8" s="14">
-        <v>626.30340000000001</v>
-      </c>
-      <c r="AD8" s="14">
-        <v>616.81569999999999</v>
+      <c r="G8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="H8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="I8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="J8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="K8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="L8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="M8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="N8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="O8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="P8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="Q8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="R8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="S8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="T8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="U8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="V8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="W8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="X8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="Z8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="AA8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="AB8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="AC8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="AD8" s="15">
+        <v>0.35</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
-      <c r="AB9" s="14"/>
-      <c r="AC9" s="14"/>
-      <c r="AD9" s="14"/>
+      <c r="C9" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>0</v>
+      </c>
+      <c r="I9" s="14">
+        <v>0</v>
+      </c>
+      <c r="J9" s="14">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14">
+        <v>0</v>
+      </c>
+      <c r="L9" s="14">
+        <v>0</v>
+      </c>
+      <c r="M9" s="14">
+        <v>0</v>
+      </c>
+      <c r="N9" s="14">
+        <v>0</v>
+      </c>
+      <c r="O9" s="14">
+        <v>0</v>
+      </c>
+      <c r="P9" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="14">
+        <v>0</v>
+      </c>
+      <c r="R9" s="14">
+        <v>0</v>
+      </c>
+      <c r="S9" s="14">
+        <v>0</v>
+      </c>
+      <c r="T9" s="14">
+        <v>0</v>
+      </c>
+      <c r="U9" s="14">
+        <v>0</v>
+      </c>
+      <c r="V9" s="14">
+        <v>0</v>
+      </c>
+      <c r="W9" s="14">
+        <v>0</v>
+      </c>
+      <c r="X9" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B10" s="11"/>

--- a/data/mini-example-resilience/Power_Demand.xlsx
+++ b/data/mini-example-resilience/Power_Demand.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175883D3-FBBB-4B29-984D-62CA3C2D5536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0173B51A-8BC7-44C7-9AD3-AB93097322ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="80">
   <si>
     <t>Power - Demand</t>
   </si>
@@ -281,6 +281,78 @@
   </si>
   <si>
     <t>Node_feedin</t>
+  </si>
+  <si>
+    <t>k0025</t>
+  </si>
+  <si>
+    <t>k0026</t>
+  </si>
+  <si>
+    <t>k0027</t>
+  </si>
+  <si>
+    <t>k0028</t>
+  </si>
+  <si>
+    <t>k0029</t>
+  </si>
+  <si>
+    <t>k0030</t>
+  </si>
+  <si>
+    <t>k0031</t>
+  </si>
+  <si>
+    <t>k0032</t>
+  </si>
+  <si>
+    <t>k0033</t>
+  </si>
+  <si>
+    <t>k0034</t>
+  </si>
+  <si>
+    <t>k0035</t>
+  </si>
+  <si>
+    <t>k0036</t>
+  </si>
+  <si>
+    <t>k0037</t>
+  </si>
+  <si>
+    <t>k0038</t>
+  </si>
+  <si>
+    <t>k0039</t>
+  </si>
+  <si>
+    <t>k0040</t>
+  </si>
+  <si>
+    <t>k0041</t>
+  </si>
+  <si>
+    <t>k0042</t>
+  </si>
+  <si>
+    <t>k0043</t>
+  </si>
+  <si>
+    <t>k0044</t>
+  </si>
+  <si>
+    <t>k0045</t>
+  </si>
+  <si>
+    <t>k0046</t>
+  </si>
+  <si>
+    <t>k0047</t>
+  </si>
+  <si>
+    <t>k0048</t>
   </si>
 </sst>
 </file>
@@ -290,7 +362,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,6 +394,12 @@
     <font>
       <sz val="11"/>
       <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -722,7 +800,7 @@
   <sheetPr>
     <tabColor rgb="FF008080"/>
   </sheetPr>
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:BG70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -732,7 +810,7 @@
     <col min="7" max="30" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:59" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -766,7 +844,7 @@
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:59" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -774,7 +852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:59" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
@@ -862,8 +940,85 @@
       <c r="AD3" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AO3" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP3" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AR3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU3" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AV3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AX3" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AY3" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AZ3" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="BA3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="BB3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC3" s="5"/>
+      <c r="BD3" s="5"/>
+      <c r="BE3" s="5"/>
+      <c r="BF3" s="5"/>
+      <c r="BG3" s="5"/>
+    </row>
+    <row r="4" spans="1:59" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>32</v>
       </c>
@@ -951,8 +1106,85 @@
       <c r="AD4" s="6" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE4" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF4" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ4" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM4" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AO4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP4" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AR4" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT4" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AV4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AX4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AY4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AZ4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="BA4" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="BB4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC4" s="6"/>
+      <c r="BD4" s="6"/>
+      <c r="BE4" s="6"/>
+      <c r="BF4" s="6"/>
+      <c r="BG4" s="6"/>
+    </row>
+    <row r="5" spans="1:59" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
         <v>36</v>
       </c>
@@ -995,7 +1227,7 @@
       <c r="AC5" s="7"/>
       <c r="AD5" s="7"/>
     </row>
-    <row r="6" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:59" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>42</v>
       </c>
@@ -1084,7 +1316,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:59" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
         <v>45</v>
       </c>
@@ -1173,7 +1405,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:59" x14ac:dyDescent="0.25">
       <c r="B8" s="11"/>
       <c r="C8" s="12" t="s">
         <v>51</v>
@@ -1206,46 +1438,46 @@
         <v>0.35</v>
       </c>
       <c r="M8" s="15">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="N8" s="15">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="O8" s="15">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="P8" s="15">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="Q8" s="15">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="R8" s="15">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="S8" s="15">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="T8" s="15">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="U8" s="15">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="V8" s="15">
-        <v>0.35</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="W8" s="15">
-        <v>0.35</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="X8" s="15">
-        <v>0.35</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="Y8" s="15">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="Z8" s="15">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="AA8" s="15">
         <v>0.35</v>
@@ -1259,8 +1491,80 @@
       <c r="AD8" s="15">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="AF8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="AG8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="AH8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="AI8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="AJ8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="AK8" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="AL8" s="15">
+        <v>0.45</v>
+      </c>
+      <c r="AM8" s="15">
+        <v>0.45</v>
+      </c>
+      <c r="AN8" s="15">
+        <v>0.45</v>
+      </c>
+      <c r="AO8" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AP8" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AQ8" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AR8" s="15">
+        <v>0.48</v>
+      </c>
+      <c r="AS8" s="15">
+        <v>0.48</v>
+      </c>
+      <c r="AT8" s="15">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AU8" s="15">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AV8" s="15">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AW8" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AX8" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="AY8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="AZ8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="BA8" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="BB8" s="15">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:59" x14ac:dyDescent="0.25">
       <c r="B9" s="11"/>
       <c r="C9" s="12" t="s">
         <v>51</v>
@@ -1346,8 +1650,80 @@
       <c r="AD9" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="14">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="14">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:59" x14ac:dyDescent="0.25">
       <c r="B10" s="11"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -1378,7 +1754,7 @@
       <c r="AC10" s="14"/>
       <c r="AD10" s="14"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:59" x14ac:dyDescent="0.25">
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -1409,7 +1785,7 @@
       <c r="AC11" s="14"/>
       <c r="AD11" s="14"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:59" x14ac:dyDescent="0.25">
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
@@ -1440,7 +1816,7 @@
       <c r="AC12" s="14"/>
       <c r="AD12" s="14"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:59" x14ac:dyDescent="0.25">
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -1471,7 +1847,7 @@
       <c r="AC13" s="14"/>
       <c r="AD13" s="14"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:59" x14ac:dyDescent="0.25">
       <c r="B14" s="11"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -1502,7 +1878,7 @@
       <c r="AC14" s="14"/>
       <c r="AD14" s="14"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:59" x14ac:dyDescent="0.25">
       <c r="B15" s="11"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -1533,7 +1909,7 @@
       <c r="AC15" s="14"/>
       <c r="AD15" s="14"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:59" x14ac:dyDescent="0.25">
       <c r="B16" s="11"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
@@ -3239,6 +3615,7 @@
       <c r="AD70" s="14"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
